--- a/02-risk-register/risk-register.xlsx
+++ b/02-risk-register/risk-register.xlsx
@@ -8,7 +8,8 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Risk Register" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Heatmap" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -20,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="83">
   <si>
     <t xml:space="preserve">Risk ID</t>
   </si>
@@ -218,6 +219,57 @@
   </si>
   <si>
     <t xml:space="preserve">Physical security controls inherited from AWS GovCloud. No LTS-owned physical assets.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Likelihood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Impact</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medium-High</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Likelihood / Impact</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R-005, R-006, R-007, R-009, R-010, R-011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Score Range</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Color</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Risk IDs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17 - 20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Red</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15 – 16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Orange</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10 - 14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yellow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R-001, R-002, R-005, R-006, R-007, R-009, R-010, R-011, R-012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Green</t>
   </si>
 </sst>
 </file>
@@ -228,7 +280,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="@"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="11">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -249,6 +301,13 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -277,8 +336,22 @@
       <family val="1"/>
       <charset val="1"/>
     </font>
+    <font>
+      <i val="true"/>
+      <sz val="10.5"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -287,8 +360,32 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFCC0000"/>
+        <bgColor rgb="FF800000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFCCECFC"/>
         <bgColor rgb="FFCCFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFD74C"/>
+        <bgColor rgb="FFFFCC99"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD36118"/>
+        <bgColor rgb="FF993300"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF18A303"/>
+        <bgColor rgb="FF339966"/>
       </patternFill>
     </fill>
   </fills>
@@ -315,7 +412,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
+  <cellStyleXfs count="21">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -339,8 +436,11 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="23">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -357,35 +457,35 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -393,31 +493,68 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="7">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Comma" xfId="15" builtinId="3"/>
     <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
     <cellStyle name="Currency" xfId="17" builtinId="4"/>
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
+    <cellStyle name="16" xfId="20"/>
   </cellStyles>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
       <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FFCC0000"/>
       <rgbColor rgb="FF00FF00"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FFFFFF00"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FF00FFFF"/>
       <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008000"/>
+      <rgbColor rgb="FF18A303"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FF808000"/>
       <rgbColor rgb="FF800080"/>
@@ -451,9 +588,9 @@
       <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF99CC00"/>
-      <rgbColor rgb="FFFFCC00"/>
+      <rgbColor rgb="FFFFD74C"/>
       <rgbColor rgb="FFFF9900"/>
-      <rgbColor rgb="FFFF6600"/>
+      <rgbColor rgb="FFD36118"/>
       <rgbColor rgb="FF666699"/>
       <rgbColor rgb="FF969696"/>
       <rgbColor rgb="FF003366"/>
@@ -1068,4 +1205,471 @@
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:F26"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="19.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13.68"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="8.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="59.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="13.4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12.01"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" s="14" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="C2" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" s="16" t="n">
+        <v>12</v>
+      </c>
+      <c r="E2" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="17" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" s="16" t="n">
+        <v>12</v>
+      </c>
+      <c r="E3" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="17" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="E4" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" s="17" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="C5" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="E5" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="F5" s="17" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="E6" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" s="17" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="E7" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="17" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="C8" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="E8" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="F8" s="17" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="B9" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="C9" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" s="16" t="n">
+        <v>16</v>
+      </c>
+      <c r="E9" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="F9" s="17" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="B10" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="C10" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="E10" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="F10" s="17" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="B11" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="C11" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="E11" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="F11" s="17" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="B12" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="C12" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="D12" s="16" t="n">
+        <v>12</v>
+      </c>
+      <c r="E12" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="F12" s="17" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="B13" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="C13" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="E13" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="F13" s="17" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="18"/>
+      <c r="B14" s="18"/>
+      <c r="C14" s="18"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="18"/>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="B15" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E15" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="F15" s="14" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="B16" s="16"/>
+      <c r="C16" s="16"/>
+      <c r="D16" s="16"/>
+      <c r="E16" s="16"/>
+      <c r="F16" s="19" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="B17" s="16"/>
+      <c r="C17" s="16"/>
+      <c r="D17" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="E17" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="F17" s="21" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="B18" s="16"/>
+      <c r="C18" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="D18" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="E18" s="16"/>
+      <c r="F18" s="16"/>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="B19" s="16"/>
+      <c r="C19" s="16"/>
+      <c r="D19" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="E19" s="16"/>
+      <c r="F19" s="16"/>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="B20" s="16"/>
+      <c r="C20" s="16"/>
+      <c r="D20" s="16"/>
+      <c r="E20" s="16"/>
+      <c r="F20" s="16"/>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="18"/>
+      <c r="B21" s="18"/>
+      <c r="C21" s="18"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="18"/>
+      <c r="F21" s="18"/>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="B22" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="C22" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="D22" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="E22" s="18"/>
+      <c r="F22" s="18"/>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="B23" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="C23" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="D23" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="E23" s="18"/>
+      <c r="F23" s="18"/>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="B24" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="C24" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="D24" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="E24" s="18"/>
+      <c r="F24" s="18"/>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B25" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="C25" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="D25" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="E25" s="18"/>
+      <c r="F25" s="18"/>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="C26" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="D26" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="E26" s="18"/>
+      <c r="F26" s="18"/>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
 </file>